--- a/content/table 2-2.xlsx
+++ b/content/table 2-2.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c72363082c40911d/桌面/Hi Hello/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_F25DC773A252ABDACC1048B969DB6D485BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3800117C-016C-4FE2-86DD-7F67B9C51A7A}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="11_F25DC773A252ABDACC1048B969DB6D485BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A59358C-3786-4E0F-8972-851FA255311B}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5835" yWindow="2595" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
   <si>
     <t>取件</t>
   </si>
@@ -187,6 +188,24 @@
   </si>
   <si>
     <t>寺由</t>
+  </si>
+  <si>
+    <t>答案</t>
+  </si>
+  <si>
+    <t>选项1</t>
+  </si>
+  <si>
+    <t>选项2</t>
+  </si>
+  <si>
+    <t>选项3</t>
+  </si>
+  <si>
+    <t>index l</t>
+  </si>
+  <si>
+    <t>index r</t>
   </si>
 </sst>
 </file>
@@ -504,262 +523,399 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+      <c r="E12">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>33</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+      <c r="E13">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>36</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>39</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>39</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+      <c r="E15">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>42</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>43</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+      <c r="E16">
+        <v>15</v>
+      </c>
+      <c r="F16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>45</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>47</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
+      <c r="E17">
+        <v>16</v>
+      </c>
+      <c r="F17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>48</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>50</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>48</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+      <c r="E18">
+        <v>17</v>
+      </c>
+      <c r="F18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>51</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>51</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>53</v>
+      </c>
+      <c r="E19">
+        <v>18</v>
+      </c>
+      <c r="F19">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E48ECF4F-76AB-42FC-BB83-50EB44611B9A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/content/table 2-2.xlsx
+++ b/content/table 2-2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c72363082c40911d/桌面/Hi Hello/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/二年级/二上/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_F25DC773A252ABDACC1048B969DB6D485BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A59358C-3786-4E0F-8972-851FA255311B}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="11_F25DC773A252ABDACC1048B969DB6D485BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7911BF1-346C-4BA9-A488-93F4F75ABBAC}"/>
   <bookViews>
-    <workbookView xWindow="5835" yWindow="2595" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,169 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
-  <si>
-    <t>取件</t>
-  </si>
-  <si>
-    <t>趣件</t>
-  </si>
-  <si>
-    <t>取见</t>
-  </si>
-  <si>
-    <t>趣味</t>
-  </si>
-  <si>
-    <t>趣位</t>
-  </si>
-  <si>
-    <t>取味</t>
-  </si>
-  <si>
-    <t>航空</t>
-  </si>
-  <si>
-    <t>杭空</t>
-  </si>
-  <si>
-    <t>行空</t>
-  </si>
-  <si>
-    <t>急忙</t>
-  </si>
-  <si>
-    <t>忘忙</t>
-  </si>
-  <si>
-    <t>稳忙</t>
-  </si>
-  <si>
-    <t>稳定</t>
-  </si>
-  <si>
-    <t>急定</t>
-  </si>
-  <si>
-    <t>隐定</t>
-  </si>
-  <si>
-    <t>舒服</t>
-  </si>
-  <si>
-    <t>舍服</t>
-  </si>
-  <si>
-    <t>舒报</t>
-  </si>
-  <si>
-    <t>宇宙</t>
-  </si>
-  <si>
-    <t>宇由</t>
-  </si>
-  <si>
-    <t>于宙</t>
-  </si>
-  <si>
-    <t>固体</t>
-  </si>
-  <si>
-    <t>古体</t>
-  </si>
-  <si>
-    <t>固休</t>
-  </si>
-  <si>
-    <t>机舱</t>
-  </si>
-  <si>
-    <t>机仓</t>
-  </si>
-  <si>
-    <t>机腔</t>
-  </si>
-  <si>
-    <t>开辟</t>
-  </si>
-  <si>
-    <t>开壁</t>
-  </si>
-  <si>
-    <t>开臂</t>
-  </si>
-  <si>
-    <t>墙壁</t>
-  </si>
-  <si>
-    <t>墙臂</t>
-  </si>
-  <si>
-    <t>墙辟</t>
-  </si>
-  <si>
-    <t>手臂</t>
-  </si>
-  <si>
-    <t>手辟</t>
-  </si>
-  <si>
-    <t>手壁</t>
-  </si>
-  <si>
-    <t>巧妙</t>
-  </si>
-  <si>
-    <t>攻妙</t>
-  </si>
-  <si>
-    <t>巧秒</t>
-  </si>
-  <si>
-    <t>移动</t>
-  </si>
-  <si>
-    <t>侈动</t>
-  </si>
-  <si>
-    <t>移冻</t>
-  </si>
-  <si>
-    <t>特别</t>
-  </si>
-  <si>
-    <t>寺别</t>
-  </si>
-  <si>
-    <t>持别</t>
-  </si>
-  <si>
-    <t>制造</t>
-  </si>
-  <si>
-    <t>制告</t>
-  </si>
-  <si>
-    <t>治造</t>
-  </si>
-  <si>
-    <t>或许</t>
-  </si>
-  <si>
-    <t>或特</t>
-  </si>
-  <si>
-    <t>或午</t>
-  </si>
-  <si>
-    <t>寺庙</t>
-  </si>
-  <si>
-    <t>特庙</t>
-  </si>
-  <si>
-    <t>寺由</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
   <si>
     <t>答案</t>
   </si>
@@ -206,6 +44,186 @@
   </si>
   <si>
     <t>index r</t>
+  </si>
+  <si>
+    <t>看见</t>
+  </si>
+  <si>
+    <t>着见</t>
+  </si>
+  <si>
+    <t>看贝</t>
+  </si>
+  <si>
+    <t>哪里</t>
+  </si>
+  <si>
+    <t>那里</t>
+  </si>
+  <si>
+    <t>哪哩</t>
+  </si>
+  <si>
+    <t>那边</t>
+  </si>
+  <si>
+    <t>哪边</t>
+  </si>
+  <si>
+    <t>那过</t>
+  </si>
+  <si>
+    <t>头顶</t>
+  </si>
+  <si>
+    <t>犬顶</t>
+  </si>
+  <si>
+    <t>头频</t>
+  </si>
+  <si>
+    <t>眼睛</t>
+  </si>
+  <si>
+    <t>眼晴</t>
+  </si>
+  <si>
+    <t>很睛</t>
+  </si>
+  <si>
+    <t>雪白</t>
+  </si>
+  <si>
+    <t>雪自</t>
+  </si>
+  <si>
+    <t>雷白</t>
+  </si>
+  <si>
+    <t>肚皮</t>
+  </si>
+  <si>
+    <t>杜皮</t>
+  </si>
+  <si>
+    <t>肚波</t>
+  </si>
+  <si>
+    <t>天空</t>
+  </si>
+  <si>
+    <t>大空</t>
+  </si>
+  <si>
+    <t>天箜</t>
+  </si>
+  <si>
+    <t>傍晚</t>
+  </si>
+  <si>
+    <t>旁晚</t>
+  </si>
+  <si>
+    <t>膀晚</t>
+  </si>
+  <si>
+    <t>冬天</t>
+  </si>
+  <si>
+    <t>佟天</t>
+  </si>
+  <si>
+    <t>东天</t>
+  </si>
+  <si>
+    <t>花朵</t>
+  </si>
+  <si>
+    <t>花垛</t>
+  </si>
+  <si>
+    <t>花剁</t>
+  </si>
+  <si>
+    <t>平常</t>
+  </si>
+  <si>
+    <t>苹常</t>
+  </si>
+  <si>
+    <t>平赏</t>
+  </si>
+  <si>
+    <t>海洋</t>
+  </si>
+  <si>
+    <t>每羊</t>
+  </si>
+  <si>
+    <t>海样</t>
+  </si>
+  <si>
+    <t>工作</t>
+  </si>
+  <si>
+    <t>王作</t>
+  </si>
+  <si>
+    <t>工做</t>
+  </si>
+  <si>
+    <t>办法</t>
+  </si>
+  <si>
+    <t>力法</t>
+  </si>
+  <si>
+    <t>为法</t>
+  </si>
+  <si>
+    <t>如果</t>
+  </si>
+  <si>
+    <t>茹果</t>
+  </si>
+  <si>
+    <t>如裹</t>
+  </si>
+  <si>
+    <t>已经</t>
+  </si>
+  <si>
+    <t>己经</t>
+  </si>
+  <si>
+    <t>已径</t>
+  </si>
+  <si>
+    <t>四海为家</t>
+  </si>
+  <si>
+    <t>四每为家</t>
+  </si>
+  <si>
+    <t>四海办家</t>
+  </si>
+  <si>
+    <t>知识</t>
+  </si>
+  <si>
+    <t>知只</t>
+  </si>
+  <si>
+    <t>治识</t>
+  </si>
+  <si>
+    <t>娃娃</t>
+  </si>
+  <si>
+    <t>挂挂</t>
+  </si>
+  <si>
+    <t>鞋鞋</t>
   </si>
 </sst>
 </file>
@@ -523,41 +541,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -566,18 +584,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -586,18 +604,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -606,18 +624,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -626,18 +644,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -646,18 +664,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -666,18 +684,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -686,18 +704,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -706,18 +724,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -726,18 +744,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -746,18 +764,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -766,18 +784,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -786,18 +804,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -806,18 +824,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -826,18 +844,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -846,18 +864,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -866,18 +884,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -886,24 +904,52 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E19">
         <v>18</v>
       </c>
       <c r="F19">
         <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -914,7 +960,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E48ECF4F-76AB-42FC-BB83-50EB44611B9A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
